--- a/docs/13. Wherehouse_고도화_주거지예약시스템/2. 문제해결/1. 테스트시나리오_1/결과/F004_측정결과.xlsx
+++ b/docs/13. Wherehouse_고도화_주거지예약시스템/2. 문제해결/1. 테스트시나리오_1/결과/F004_측정결과.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>■ 회차 정보</t>
+          <t>■ 회차 정보 / 측정 환경</t>
         </is>
       </c>
     </row>
@@ -612,357 +612,425 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>■ 동시 요청의 단계별 통과 분포</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>측정 지점</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>1_unique적용</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>2_unique제거</t>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>격리</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>READ COMMITTED</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>READ COMMITTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Propagation</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>UQ제약</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>적용</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>제거</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>동시성제어</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>DB 부분 유일 인덱스</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>없음 (baseline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 동시 요청의 단계별 통과 분포</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>측정 지점</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>1_unique적용</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2_unique제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>확인 조회 통과 (슬롯을 "예약 가능" 으로 인지)</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B17" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C17" s="6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>점유 통과 (슬롯을 "예약됨" 으로 UPDATE 성공)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B18" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C18" s="6" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>등록 통과 (예약 INSERT 성공)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>■ 정합성 (비즈니스 규칙 1 — 슬롯당 확정 예약 = 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>1_unique적용</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2_unique제거</t>
-        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>등록 통과 (예약 INSERT 성공)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 정합성 (비즈니스 규칙 1 — 슬롯당 확정 예약 = 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>1_unique적용</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2_unique제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>CONFIRMED 행 수 (DB 에 남은 확정 예약)</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>슬롯당 동시 관측된 최대 CONFIRMED 수</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B24" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C24" s="9" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>정합성 위반 요청 수 (등록 후 예약 수 ≥ 2 로 관측)</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>■ DB 단 거부 발생 (부분 유일 인덱스 UQ_VISIT_RESERVATION_CONFIRMED_SLOT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>이벤트</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>1_unique적용</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>2_unique제거</t>
-        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>정합성 위반 요청 수 (등록 후 예약 수 ≥ 2 로 관측)</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>■ DB 단 거부 발생 (부분 유일 인덱스 UQ_VISIT_RESERVATION_CONFIRMED_SLOT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>이벤트</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>1_unique적용</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2_unique제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>DB 무결성 위반 처리 진입 수 ([VISIT_INTEGRITY_BACKSTOP] 로그)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B29" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C29" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>ORA-00001 발생 수 (UQ_VISIT_RESERVATION_CONFIRMED_SLOT 등)</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B30" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C30" s="6" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>그 외 ORA-xxxxx 발생 수</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>■ 확인→등록 응답시간 (확인 조회 직후 → 등록 직후 구간, 등록까지 도달한 요청 한정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>통계 항목</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>1_unique적용</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>2_unique제거</t>
-        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>그 외 ORA-xxxxx 발생 수</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>■ 확인→등록 응답시간 (확인 조회 직후 → 등록 직후 구간, 등록까지 도달한 요청 한정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>통계 항목</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>1_unique적용</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2_unique제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>평균</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>70,176,600 ns  (≈ 70.18 ms)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>45,215,780 ns  (≈ 45.22 ms)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>최솟값</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>70,176,600 ns  (≈ 70.18 ms)</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>42,766,000 ns  (≈ 42.77 ms)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>최댓값</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>70,176,600 ns  (≈ 70.18 ms)</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>54,777,800 ns  (≈ 54.78 ms)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>표준편차</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>5,345,534 ns  (≈ 5.35 ms)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>■ 본 시트 해석 가이드</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>확인 조회 통과 = 총 요청 수</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>같은 슬롯에 동시 요청한 N 건 모두 슬롯을 "예약 가능" 으로 인지한 것이다. 즉 확인 조회와 상태 변경 사이의 시간 간격에서 동시 N 건이 모두 같은 옛 값을 본다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>점유 통과 = 총 요청 수</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>N 건 모두 슬롯 상태를 "예약됨" 으로 UPDATE 성공한 것이다. Oracle 의 자동 행 락은 N 개 UPDATE 를 순차로 실행시킬 뿐 두 번째 UPDATE 를 거부하지는 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>등록 통과 = 1 vs N</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>예약 INSERT 단계의 통과 인원. 1 이라면 DB 단의 부분 유일 인덱스가 후속 트랜잭션을 거부한 것이고, N 이라면 추가 메커니즘 없이 모두 INSERT 됨 — 한 슬롯에 N 명 확정 (정합성 위반) 의 직접 관측.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>CONFIRMED 행 수 / 슬롯당 최대 관측</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>"CONFIRMED 행 수" 는 측정 종료 후 DB 잔여. "슬롯당 최대 관측" 은 측정 중 어느 한 트랜잭션이 등록 직후 시점에 관측한 동일 슬롯의 누적 예약 수 최댓값. 둘 다 1 이어야 비즈니스 규칙 1 충족.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>DB 무결성 위반 처리 진입 = N-1</t>
+          <t>확인 조회 통과 = 총 요청 수</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>예약 INSERT 단계에서 부분 유일 인덱스가 N-1 건을 ORA-00001 로 거부했다는 의미. 이 값이 N-1 이면 DB 단 보호망 활성, 0 이면 비활성 환경.</t>
+          <t>같은 슬롯에 동시 요청한 N 건 모두 슬롯을 "예약 가능" 으로 인지한 것이다. 즉 확인 조회와 상태 변경 사이의 시간 간격에서 동시 N 건이 모두 같은 옛 값을 본다.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>점유 통과 = 총 요청 수</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>N 건 모두 슬롯 상태를 "예약됨" 으로 UPDATE 성공한 것이다. Oracle 의 자동 행 락은 N 개 UPDATE 를 순차로 실행시킬 뿐 두 번째 UPDATE 를 거부하지는 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>등록 통과 = 1 vs N</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>예약 INSERT 단계의 통과 인원. 1 이라면 DB 단의 부분 유일 인덱스가 후속 트랜잭션을 거부한 것이고, N 이라면 추가 메커니즘 없이 모두 INSERT 됨 — 한 슬롯에 N 명 확정 (정합성 위반) 의 직접 관측.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED 행 수 / 슬롯당 최대 관측</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>"CONFIRMED 행 수" 는 측정 종료 후 DB 잔여. "슬롯당 최대 관측" 은 측정 중 어느 한 트랜잭션이 등록 직후 시점에 관측한 동일 슬롯의 누적 예약 수 최댓값. 둘 다 1 이어야 비즈니스 규칙 1 충족.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>DB 무결성 위반 처리 진입 = N-1</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>예약 INSERT 단계에서 부분 유일 인덱스가 N-1 건을 ORA-00001 로 거부했다는 의미. 이 값이 N-1 이면 DB 단 보호망 활성, 0 이면 비활성 환경.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
           <t>응답시간이 회차마다 다른 의미</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>DB 단 보호망이 활성인 회차에서는 거부된 트랜잭션의 ORA-00001 처리 비용이 일부 포함되어 분산이 커진다. 비활성 회차에서는 모두 같은 코드 경로를 통과해 분산이 작다.</t>
         </is>
@@ -970,18 +1038,18 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B47:C47"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="B43:C43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
